--- a/output_pdfs/n_r_10_n_converted.xlsx
+++ b/output_pdfs/n_r_10_n_converted.xlsx
@@ -571,7 +571,7 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2/1/23</t>
+          <t>02/01/2023</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -596,7 +596,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>3/1/23</t>
+          <t>03/01/2023</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -621,7 +621,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>4/1/23</t>
+          <t>04/01/2023</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -646,7 +646,7 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>9/1/23</t>
+          <t>09/01/2023</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -671,7 +671,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>10/1/23</t>
+          <t>10/01/2023</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -696,7 +696,7 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>11/1/23</t>
+          <t>11/01/2023</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>15/1/23</t>
+          <t>15/01/2023</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -746,7 +746,7 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>16/1/23</t>
+          <t>16/01/2023</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -771,12 +771,12 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>18/11/23</t>
+          <t>18/01/2023</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>שבת</t>
+          <t>רביעי</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -796,7 +796,7 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>19/1/23</t>
+          <t>19/01/2023</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -821,7 +821,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>22/1/23</t>
+          <t>22/01/2023</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -846,7 +846,7 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>23/1/23</t>
+          <t>23/01/2023</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -871,12 +871,12 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>24/11/23</t>
+          <t>24/01/2023</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>שישי</t>
+          <t>שלישי</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -896,7 +896,7 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>25/1/23</t>
+          <t>25/01/2023</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -921,7 +921,7 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>26/1/23</t>
+          <t>26/01/2023</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
@@ -946,7 +946,7 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>29/1/23</t>
+          <t>29/01/2023</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -971,7 +971,7 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>30/1/23</t>
+          <t>30/01/2023</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -996,7 +996,7 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>31/1/23</t>
+          <t>31/01/2023</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">

--- a/output_pdfs/n_r_10_n_converted.xlsx
+++ b/output_pdfs/n_r_10_n_converted.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="דוח נוכחות חודשי" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="דוח נוכחות חודשי" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
